--- a/Inventario_Rutas_Maule_Completo.xlsx
+++ b/Inventario_Rutas_Maule_Completo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joset\OneDrive\Desktop\Nueva carpeta (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7F9B30-97EC-43E6-9573-F8F9FCEE4349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA25859-6995-4D9C-B1B1-F81C48A5CE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="135">
   <si>
     <t>Rol</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Provincia</t>
   </si>
   <si>
-    <t>Capa de Rodadura</t>
-  </si>
-  <si>
     <t>Kilometro inicial</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>Curicó</t>
   </si>
   <si>
-    <t>Asfalto</t>
-  </si>
-  <si>
     <t>J-25</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
     <t>J-446</t>
   </si>
   <si>
-    <t>Capa de protección asfáltica</t>
-  </si>
-  <si>
     <t>J-448</t>
   </si>
   <si>
@@ -91,9 +82,6 @@
     <t>J-591</t>
   </si>
   <si>
-    <t>Capa granular estabilizada</t>
-  </si>
-  <si>
     <t>J-60</t>
   </si>
   <si>
@@ -127,9 +115,6 @@
     <t>J-75-K</t>
   </si>
   <si>
-    <t>Hormigón</t>
-  </si>
-  <si>
     <t>J-76-K</t>
   </si>
   <si>
@@ -236,9 +221,6 @@
   </si>
   <si>
     <t>K-688</t>
-  </si>
-  <si>
-    <t>Sin Información</t>
   </si>
   <si>
     <t>K-78-M</t>
@@ -518,7 +500,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1834,19 +1816,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1865,3270 +1846,2904 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
+      <c r="C2">
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10.451000000000001</v>
       </c>
       <c r="E2">
         <v>10.451000000000001</v>
       </c>
       <c r="F2">
-        <v>10.451000000000001</v>
-      </c>
-      <c r="G2">
         <v>40.94</v>
       </c>
-      <c r="H2" s="3">
+      <c r="G2" s="3">
         <f>LOOKUP(A2,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>7619.0483645064787</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>23.78</v>
       </c>
       <c r="E3">
         <v>23.78</v>
       </c>
       <c r="F3">
-        <v>23.78</v>
-      </c>
-      <c r="G3">
         <v>40.94</v>
       </c>
-      <c r="H3" s="3">
+      <c r="G3" s="3">
         <f>LOOKUP(A3,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>10351.93701813308</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>20.536000000000001</v>
       </c>
       <c r="E4">
         <v>20.536000000000001</v>
       </c>
       <c r="F4">
-        <v>20.536000000000001</v>
-      </c>
-      <c r="G4">
         <v>40.94</v>
       </c>
-      <c r="H4" s="3">
+      <c r="G4" s="3">
         <f>LOOKUP(A4,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>72200.438137957812</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="E5">
         <v>10.5</v>
       </c>
       <c r="F5">
-        <v>10.5</v>
-      </c>
-      <c r="G5">
         <v>40.94</v>
       </c>
-      <c r="H5" s="3">
+      <c r="G5" s="3">
         <f>LOOKUP(A5,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>6317.4165120732696</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="E6">
         <v>5.8</v>
       </c>
       <c r="F6">
-        <v>5.8</v>
-      </c>
-      <c r="G6">
         <v>40.94</v>
       </c>
-      <c r="H6" s="3">
+      <c r="G6" s="3">
         <f>LOOKUP(A6,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2262.6284902330058</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>6.4470000000000001</v>
       </c>
       <c r="E7">
         <v>6.4470000000000001</v>
       </c>
       <c r="F7">
-        <v>6.4470000000000001</v>
-      </c>
-      <c r="G7">
         <v>40.94</v>
       </c>
-      <c r="H7" s="3">
+      <c r="G7" s="3">
         <f>LOOKUP(A7,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>10164.07724344292</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>49.69</v>
       </c>
       <c r="E8">
         <v>49.69</v>
       </c>
       <c r="F8">
-        <v>49.69</v>
-      </c>
-      <c r="G8">
         <v>40.94</v>
       </c>
-      <c r="H8" s="3">
+      <c r="G8" s="3">
         <f>LOOKUP(A8,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>19368.336953576742</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>25.22</v>
       </c>
       <c r="E9">
         <v>25.22</v>
       </c>
       <c r="F9">
-        <v>25.22</v>
-      </c>
-      <c r="G9">
         <v>40.94</v>
       </c>
-      <c r="H9" s="3">
+      <c r="G9" s="3">
         <f>LOOKUP(A9,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>49815.50482857976</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>7.3140000000000001</v>
       </c>
       <c r="E10">
         <v>7.3140000000000001</v>
       </c>
       <c r="F10">
-        <v>7.3140000000000001</v>
-      </c>
-      <c r="G10">
         <v>40.94</v>
       </c>
-      <c r="H10" s="3">
+      <c r="G10" s="3">
         <f>LOOKUP(A10,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>12250.26732338182</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>7.6840000000000002</v>
       </c>
       <c r="E11">
         <v>7.6840000000000002</v>
       </c>
       <c r="F11">
-        <v>7.6840000000000002</v>
-      </c>
-      <c r="G11">
         <v>40.94</v>
       </c>
-      <c r="H11" s="3">
+      <c r="G11" s="3">
         <f>LOOKUP(A11,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>4948.1140912628043</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>3.9849999999999999</v>
       </c>
       <c r="E12">
         <v>3.9849999999999999</v>
       </c>
       <c r="F12">
-        <v>3.9849999999999999</v>
-      </c>
-      <c r="G12">
         <v>40.94</v>
       </c>
-      <c r="H12" s="3">
+      <c r="G12" s="3">
         <f>LOOKUP(A12,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1582.373909739084</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>11.053000000000001</v>
       </c>
       <c r="E13">
         <v>11.053000000000001</v>
       </c>
       <c r="F13">
-        <v>11.053000000000001</v>
-      </c>
-      <c r="G13">
         <v>40.94</v>
       </c>
-      <c r="H13" s="3">
+      <c r="G13" s="3">
         <f>LOOKUP(A13,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1367.6966510538639</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>130.24</v>
       </c>
       <c r="E14">
         <v>130.24</v>
       </c>
       <c r="F14">
-        <v>130.24</v>
-      </c>
-      <c r="G14">
         <v>40.94</v>
       </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3">
         <f>LOOKUP(A14,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>93919.524354428388</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="E15">
         <v>11.2</v>
       </c>
       <c r="F15">
-        <v>11.2</v>
-      </c>
-      <c r="G15">
         <v>40.94</v>
       </c>
-      <c r="H15" s="3">
+      <c r="G15" s="3">
         <f>LOOKUP(A15,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>11948.086781785079</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E16">
         <v>2.7</v>
       </c>
       <c r="F16">
-        <v>2.7</v>
-      </c>
-      <c r="G16">
         <v>40.94</v>
       </c>
-      <c r="H16" s="3">
+      <c r="G16" s="3">
         <f>LOOKUP(A16,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>189548.06202502971</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>3.1349999999999998</v>
       </c>
       <c r="E17">
         <v>3.1349999999999998</v>
       </c>
       <c r="F17">
-        <v>3.1349999999999998</v>
-      </c>
-      <c r="G17">
         <v>40.94</v>
       </c>
-      <c r="H17" s="3">
+      <c r="G17" s="3">
         <f>LOOKUP(A17,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>3988.1309129103861</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="E18">
         <v>9.25</v>
       </c>
       <c r="F18">
-        <v>9.25</v>
-      </c>
-      <c r="G18">
         <v>40.94</v>
       </c>
-      <c r="H18" s="3">
+      <c r="G18" s="3">
         <f>LOOKUP(A18,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>3371.0139577269729</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="E19">
         <v>24.8</v>
       </c>
       <c r="F19">
-        <v>24.8</v>
-      </c>
-      <c r="G19">
         <v>40.94</v>
       </c>
-      <c r="H19" s="3">
+      <c r="G19" s="3">
         <f>LOOKUP(A19,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>43024.962376204312</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="E20">
         <v>9.6</v>
       </c>
       <c r="F20">
-        <v>9.6</v>
-      </c>
-      <c r="G20">
         <v>40.94</v>
       </c>
-      <c r="H20" s="3">
+      <c r="G20" s="3">
         <f>LOOKUP(A20,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>5329.4229054158404</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>39.475999999999999</v>
       </c>
       <c r="E21">
         <v>39.475999999999999</v>
       </c>
       <c r="F21">
-        <v>39.475999999999999</v>
-      </c>
-      <c r="G21">
         <v>40.94</v>
       </c>
-      <c r="H21" s="3">
+      <c r="G21" s="3">
         <f>LOOKUP(A21,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1304.771666666667</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="E22">
         <v>1.27</v>
       </c>
       <c r="F22">
-        <v>1.27</v>
-      </c>
-      <c r="G22">
         <v>40.94</v>
       </c>
-      <c r="H22" s="3">
+      <c r="G22" s="3">
         <f>LOOKUP(A22,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>8217.7890665854538</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>25.65</v>
       </c>
       <c r="E23">
         <v>25.65</v>
       </c>
       <c r="F23">
-        <v>25.65</v>
-      </c>
-      <c r="G23">
         <v>40.94</v>
       </c>
-      <c r="H23" s="3">
+      <c r="G23" s="3">
         <f>LOOKUP(A23,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>5581.8228093440794</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>34</v>
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>76.295000000000002</v>
       </c>
       <c r="E24">
         <v>76.295000000000002</v>
       </c>
       <c r="F24">
-        <v>76.295000000000002</v>
-      </c>
-      <c r="G24">
         <v>40.94</v>
       </c>
-      <c r="H24" s="3">
+      <c r="G24" s="3">
         <f>LOOKUP(A24,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>21831.927681984271</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>55.051000000000002</v>
       </c>
       <c r="E25">
         <v>55.051000000000002</v>
       </c>
       <c r="F25">
-        <v>55.051000000000002</v>
-      </c>
-      <c r="G25">
         <v>40.94</v>
       </c>
-      <c r="H25" s="3">
+      <c r="G25" s="3">
         <f>LOOKUP(A25,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>52757.050324769218</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>3.8620000000000001</v>
       </c>
       <c r="E26">
         <v>3.8620000000000001</v>
       </c>
       <c r="F26">
-        <v>3.8620000000000001</v>
-      </c>
-      <c r="G26">
         <v>40.94</v>
       </c>
-      <c r="H26" s="3">
+      <c r="G26" s="3">
         <f>LOOKUP(A26,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>9361.7908776452696</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>38.795000000000002</v>
       </c>
       <c r="E27">
         <v>38.795000000000002</v>
       </c>
       <c r="F27">
-        <v>38.795000000000002</v>
-      </c>
-      <c r="G27">
         <v>40.94</v>
       </c>
-      <c r="H27" s="3">
+      <c r="G27" s="3">
         <f>LOOKUP(A27,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>13815.300838874749</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>16.254999999999999</v>
       </c>
       <c r="E28">
         <v>16.254999999999999</v>
       </c>
       <c r="F28">
-        <v>16.254999999999999</v>
-      </c>
-      <c r="G28">
         <v>40.94</v>
       </c>
-      <c r="H28" s="3">
+      <c r="G28" s="3">
         <f>LOOKUP(A28,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1435.3962969289489</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1.829</v>
       </c>
       <c r="E29">
         <v>1.829</v>
       </c>
       <c r="F29">
-        <v>1.829</v>
-      </c>
-      <c r="G29">
         <v>40.94</v>
       </c>
-      <c r="H29" s="3">
+      <c r="G29" s="3">
         <f>LOOKUP(A29,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>900.52823916286729</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>12.57</v>
       </c>
       <c r="E30">
         <v>12.57</v>
       </c>
       <c r="F30">
-        <v>12.57</v>
-      </c>
-      <c r="G30">
         <v>40.94</v>
       </c>
-      <c r="H30" s="3">
+      <c r="G30" s="3">
         <f>LOOKUP(A30,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>6234.0746979889091</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="E31">
         <v>7.65</v>
       </c>
       <c r="F31">
-        <v>7.65</v>
-      </c>
-      <c r="G31">
         <v>40.94</v>
       </c>
-      <c r="H31" s="3">
+      <c r="G31" s="3">
         <f>LOOKUP(A31,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>3242.3081745541072</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="E32">
         <v>0.35</v>
       </c>
       <c r="F32">
-        <v>0.35</v>
-      </c>
-      <c r="G32">
         <v>40.94</v>
       </c>
-      <c r="H32" s="3">
+      <c r="G32" s="3">
         <f>LOOKUP(A32,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>482.37910440169452</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>28.303999999999998</v>
       </c>
       <c r="E33">
         <v>28.303999999999998</v>
       </c>
       <c r="F33">
-        <v>28.303999999999998</v>
-      </c>
-      <c r="G33">
         <v>43.05</v>
       </c>
-      <c r="H33" s="3">
+      <c r="G33" s="3">
         <f>LOOKUP(A33,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>5992.2399058473693</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>28.837</v>
       </c>
       <c r="E34">
         <v>28.837</v>
       </c>
       <c r="F34">
-        <v>28.837</v>
-      </c>
-      <c r="G34">
         <v>43.05</v>
       </c>
-      <c r="H34" s="3">
+      <c r="G34" s="3">
         <f>LOOKUP(A34,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1082.474698389354</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>21.170999999999999</v>
       </c>
       <c r="E35">
         <v>21.170999999999999</v>
       </c>
       <c r="F35">
-        <v>21.170999999999999</v>
-      </c>
-      <c r="G35">
         <v>43.05</v>
       </c>
-      <c r="H35" s="3">
+      <c r="G35" s="3">
         <f>LOOKUP(A35,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>7717.1002948804489</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>12.05</v>
       </c>
       <c r="E36">
         <v>12.05</v>
       </c>
       <c r="F36">
-        <v>12.05</v>
-      </c>
-      <c r="G36">
         <v>43.04999999999999</v>
       </c>
-      <c r="H36" s="3">
+      <c r="G36" s="3">
         <f>LOOKUP(A36,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>726.85382758346645</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>37.557000000000002</v>
       </c>
       <c r="E37">
         <v>37.557000000000002</v>
       </c>
       <c r="F37">
-        <v>37.557000000000002</v>
-      </c>
-      <c r="G37">
         <v>43.05</v>
       </c>
-      <c r="H37" s="3">
+      <c r="G37" s="3">
         <f>LOOKUP(A37,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>4104.2270222378784</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>8.61</v>
       </c>
       <c r="E38">
         <v>8.61</v>
       </c>
       <c r="F38">
-        <v>8.61</v>
-      </c>
-      <c r="G38">
         <v>43.05</v>
       </c>
-      <c r="H38" s="3">
+      <c r="G38" s="3">
         <f>LOOKUP(A38,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>830.36812317638282</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>24.321000000000002</v>
       </c>
       <c r="E39">
         <v>24.321000000000002</v>
       </c>
       <c r="F39">
-        <v>24.321000000000002</v>
-      </c>
-      <c r="G39">
         <v>43.05</v>
       </c>
-      <c r="H39" s="3">
+      <c r="G39" s="3">
         <f>LOOKUP(A39,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>976.76167199999998</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>14.63</v>
       </c>
       <c r="E40">
         <v>14.63</v>
       </c>
       <c r="F40">
-        <v>14.63</v>
-      </c>
-      <c r="G40">
         <v>43.05</v>
       </c>
-      <c r="H40" s="3">
+      <c r="G40" s="3">
         <f>LOOKUP(A40,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>179431.96411190819</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="E41">
         <v>36.299999999999997</v>
       </c>
       <c r="F41">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="G41">
         <v>43.05</v>
       </c>
-      <c r="H41" s="3">
+      <c r="G41" s="3">
         <f>LOOKUP(A41,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>19630.131033602502</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>11.311999999999999</v>
       </c>
       <c r="E42">
         <v>11.311999999999999</v>
       </c>
       <c r="F42">
-        <v>11.311999999999999</v>
-      </c>
-      <c r="G42">
         <v>43.05</v>
       </c>
-      <c r="H42" s="3">
+      <c r="G42" s="3">
         <f>LOOKUP(A42,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1791.3023261411879</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="E43">
         <v>36.159999999999997</v>
       </c>
       <c r="F43">
-        <v>36.159999999999997</v>
-      </c>
-      <c r="G43">
         <v>43.04999999999999</v>
       </c>
-      <c r="H43" s="3">
+      <c r="G43" s="3">
         <f>LOOKUP(A43,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>724.45718474620548</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>30.164000000000001</v>
       </c>
       <c r="E44">
         <v>30.164000000000001</v>
       </c>
       <c r="F44">
-        <v>30.164000000000001</v>
-      </c>
-      <c r="G44">
         <v>43.05</v>
       </c>
-      <c r="H44" s="3">
+      <c r="G44" s="3">
         <f>LOOKUP(A44,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>67846.952110057697</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>10.991</v>
       </c>
       <c r="E45">
         <v>10.991</v>
       </c>
       <c r="F45">
-        <v>10.991</v>
-      </c>
-      <c r="G45">
         <v>43.05</v>
       </c>
-      <c r="H45" s="3">
+      <c r="G45" s="3">
         <f>LOOKUP(A45,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>5567.75982729321</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="E46">
         <v>8.1300000000000008</v>
       </c>
       <c r="F46">
-        <v>8.1300000000000008</v>
-      </c>
-      <c r="G46">
         <v>43.05</v>
       </c>
-      <c r="H46" s="3">
+      <c r="G46" s="3">
         <f>LOOKUP(A46,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>3532.2193312939939</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C47" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>10.536</v>
       </c>
       <c r="E47">
         <v>10.536</v>
       </c>
       <c r="F47">
-        <v>10.536</v>
-      </c>
-      <c r="G47">
         <v>43.05</v>
       </c>
-      <c r="H47" s="3">
+      <c r="G47" s="3">
         <f>LOOKUP(A47,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1992.403732324485</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C48" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>8.5259999999999998</v>
       </c>
       <c r="E48">
         <v>8.5259999999999998</v>
       </c>
       <c r="F48">
-        <v>8.5259999999999998</v>
-      </c>
-      <c r="G48">
         <v>43.05</v>
       </c>
-      <c r="H48" s="3">
+      <c r="G48" s="3">
         <f>LOOKUP(A48,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>850.71241505968783</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="E49">
         <v>6.42</v>
       </c>
       <c r="F49">
-        <v>6.42</v>
-      </c>
-      <c r="G49">
         <v>43.05</v>
       </c>
-      <c r="H49" s="3">
+      <c r="G49" s="3">
         <f>LOOKUP(A49,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2390.432140429954</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>31.658999999999999</v>
       </c>
       <c r="E50">
         <v>31.658999999999999</v>
       </c>
       <c r="F50">
-        <v>31.658999999999999</v>
-      </c>
-      <c r="G50">
         <v>43.04999999999999</v>
       </c>
-      <c r="H50" s="3">
+      <c r="G50" s="3">
         <f>LOOKUP(A50,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>25422.034201961818</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="E51">
         <v>14.6</v>
       </c>
       <c r="F51">
-        <v>14.6</v>
-      </c>
-      <c r="G51">
         <v>43.05</v>
       </c>
-      <c r="H51" s="3">
+      <c r="G51" s="3">
         <f>LOOKUP(A51,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>25422.034201961818</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>5.0279999999999996</v>
       </c>
       <c r="E52">
         <v>5.0279999999999996</v>
       </c>
       <c r="F52">
-        <v>5.0279999999999996</v>
-      </c>
-      <c r="G52">
         <v>43.05</v>
       </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3">
         <f>LOOKUP(A52,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>3097.7968420897369</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="E53">
         <v>2.9</v>
       </c>
       <c r="F53">
-        <v>2.9</v>
-      </c>
-      <c r="G53">
         <v>43.05</v>
       </c>
-      <c r="H53" s="3">
+      <c r="G53" s="3">
         <f>LOOKUP(A53,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2447.8561655805638</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="E54">
         <v>14.4</v>
       </c>
       <c r="F54">
-        <v>14.4</v>
-      </c>
-      <c r="G54">
         <v>43.05</v>
       </c>
-      <c r="H54" s="3">
+      <c r="G54" s="3">
         <f>LOOKUP(A54,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>9855.9842995581421</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
-      </c>
-      <c r="C55" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>26.553999999999998</v>
       </c>
       <c r="E55">
         <v>26.553999999999998</v>
       </c>
       <c r="F55">
-        <v>26.553999999999998</v>
-      </c>
-      <c r="G55">
         <v>43.05</v>
       </c>
-      <c r="H55" s="3">
+      <c r="G55" s="3">
         <f>LOOKUP(A55,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>12856.677238693061</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
-      </c>
-      <c r="C56" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2.7229999999999999</v>
       </c>
       <c r="E56">
         <v>2.7229999999999999</v>
       </c>
       <c r="F56">
-        <v>2.7229999999999999</v>
-      </c>
-      <c r="G56">
         <v>43.05</v>
       </c>
-      <c r="H56" s="3">
+      <c r="G56" s="3">
         <f>LOOKUP(A56,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>7085.7481211057466</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
-      </c>
-      <c r="C57" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>81.382000000000005</v>
       </c>
       <c r="E57">
         <v>81.382000000000005</v>
       </c>
       <c r="F57">
-        <v>81.382000000000005</v>
-      </c>
-      <c r="G57">
         <v>43.05</v>
       </c>
-      <c r="H57" s="3">
+      <c r="G57" s="3">
         <f>LOOKUP(A57,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>55734.761525780843</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
-      </c>
-      <c r="C58" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E58">
         <v>0.8</v>
       </c>
       <c r="F58">
-        <v>0.8</v>
-      </c>
-      <c r="G58">
         <v>43.05</v>
       </c>
-      <c r="H58" s="3">
+      <c r="G58" s="3">
         <f>LOOKUP(A58,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>8959.5249647001529</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="G59">
+        <v>39</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>43.05</v>
       </c>
-      <c r="H59" s="3">
+      <c r="G59" s="3">
         <f>LOOKUP(A59,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>44.585141077055283</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
-      </c>
-      <c r="C60" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="E60">
         <v>49.3</v>
       </c>
       <c r="F60">
-        <v>49.3</v>
-      </c>
-      <c r="G60">
         <v>43.04999999999999</v>
       </c>
-      <c r="H60" s="3">
+      <c r="G60" s="3">
         <f>LOOKUP(A60,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>69495.254216778834</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" t="s">
-        <v>34</v>
+        <v>68</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>62.503999999999998</v>
       </c>
       <c r="E61">
         <v>62.503999999999998</v>
       </c>
       <c r="F61">
-        <v>62.503999999999998</v>
-      </c>
-      <c r="G61">
         <v>43.4</v>
       </c>
-      <c r="H61" s="3">
+      <c r="G61" s="3">
         <f>LOOKUP(A61,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>30951.33420428856</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="E62">
         <v>10.050000000000001</v>
       </c>
       <c r="F62">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="G62">
         <v>43.4</v>
       </c>
-      <c r="H62" s="3">
+      <c r="G62" s="3">
         <f>LOOKUP(A62,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>4102.2215134370581</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
-      </c>
-      <c r="C63" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>12.26</v>
       </c>
       <c r="E63">
         <v>12.26</v>
       </c>
       <c r="F63">
-        <v>12.26</v>
-      </c>
-      <c r="G63">
         <v>43.4</v>
       </c>
-      <c r="H63" s="3">
+      <c r="G63" s="3">
         <f>LOOKUP(A63,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>7665.1918300325251</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E64">
         <v>19</v>
       </c>
       <c r="F64">
-        <v>19</v>
-      </c>
-      <c r="G64">
         <v>43.4</v>
       </c>
-      <c r="H64" s="3">
+      <c r="G64" s="3">
         <f>LOOKUP(A64,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>49652.707851877531</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
-      </c>
-      <c r="C65" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>7.0990000000000002</v>
       </c>
       <c r="E65">
         <v>7.0990000000000002</v>
       </c>
       <c r="F65">
-        <v>7.0990000000000002</v>
-      </c>
-      <c r="G65">
         <v>43.4</v>
       </c>
-      <c r="H65" s="3">
+      <c r="G65" s="3">
         <f>LOOKUP(A65,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1649.9862670250361</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>16.68</v>
       </c>
       <c r="E66">
         <v>16.68</v>
       </c>
       <c r="F66">
-        <v>16.68</v>
-      </c>
-      <c r="G66">
         <v>43.4</v>
       </c>
-      <c r="H66" s="3">
+      <c r="G66" s="3">
         <f>LOOKUP(A66,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>5573.9897451540292</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E67">
         <v>11</v>
       </c>
       <c r="F67">
-        <v>11</v>
-      </c>
-      <c r="G67">
         <v>43.4</v>
       </c>
-      <c r="H67" s="3">
+      <c r="G67" s="3">
         <f>LOOKUP(A67,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>6717.8558496128171</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
-      </c>
-      <c r="C68" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>11.34</v>
       </c>
       <c r="E68">
         <v>11.34</v>
       </c>
       <c r="F68">
-        <v>11.34</v>
-      </c>
-      <c r="G68">
         <v>43.4</v>
       </c>
-      <c r="H68" s="3">
+      <c r="G68" s="3">
         <f>LOOKUP(A68,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>3673.9642246980379</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
-      </c>
-      <c r="C69" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2.9569999999999999</v>
       </c>
       <c r="E69">
         <v>2.9569999999999999</v>
       </c>
       <c r="F69">
-        <v>2.9569999999999999</v>
-      </c>
-      <c r="G69">
         <v>43.4</v>
       </c>
-      <c r="H69" s="3">
+      <c r="G69" s="3">
         <f>LOOKUP(A69,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>253.85420844413801</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
-      </c>
-      <c r="C70" t="s">
-        <v>34</v>
+        <v>68</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>30.02</v>
       </c>
       <c r="E70">
         <v>30.02</v>
       </c>
       <c r="F70">
-        <v>30.02</v>
-      </c>
-      <c r="G70">
         <v>43.4</v>
       </c>
-      <c r="H70" s="3">
+      <c r="G70" s="3">
         <f>LOOKUP(A70,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>35665.43809510018</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
-      </c>
-      <c r="C71" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="E71">
         <v>2.59</v>
       </c>
       <c r="F71">
-        <v>2.59</v>
-      </c>
-      <c r="G71">
         <v>43.4</v>
       </c>
-      <c r="H71" s="3">
+      <c r="G71" s="3">
         <f>LOOKUP(A71,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>5089.8657090909073</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
-      </c>
-      <c r="C72" t="s">
-        <v>22</v>
+        <v>68</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>5.4960000000000004</v>
       </c>
       <c r="E72">
         <v>5.4960000000000004</v>
       </c>
       <c r="F72">
-        <v>5.4960000000000004</v>
-      </c>
-      <c r="G72">
         <v>43.4</v>
       </c>
-      <c r="H72" s="3">
+      <c r="G72" s="3">
         <f>LOOKUP(A72,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2807.8942847058411</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>85.578999999999994</v>
       </c>
       <c r="E73">
         <v>85.578999999999994</v>
       </c>
       <c r="F73">
-        <v>85.578999999999994</v>
-      </c>
-      <c r="G73">
         <v>43.4</v>
       </c>
-      <c r="H73" s="3">
+      <c r="G73" s="3">
         <f>LOOKUP(A73,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>149104.5441978325</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C74" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>27.61</v>
       </c>
       <c r="E74">
         <v>27.61</v>
       </c>
       <c r="F74">
-        <v>27.61</v>
-      </c>
-      <c r="G74">
         <v>43.4</v>
       </c>
-      <c r="H74" s="3">
+      <c r="G74" s="3">
         <f>LOOKUP(A74,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>9449.1127267722532</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C75" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>30.425000000000001</v>
       </c>
       <c r="E75">
         <v>30.425000000000001</v>
       </c>
       <c r="F75">
-        <v>30.425000000000001</v>
-      </c>
-      <c r="G75">
         <v>43.4</v>
       </c>
-      <c r="H75" s="3">
+      <c r="G75" s="3">
         <f>LOOKUP(A75,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>15335.356975078999</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="E76">
         <v>5.45</v>
       </c>
       <c r="F76">
-        <v>5.45</v>
-      </c>
-      <c r="G76">
         <v>43.4</v>
       </c>
-      <c r="H76" s="3">
+      <c r="G76" s="3">
         <f>LOOKUP(A76,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1355.5832818502481</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>13.74</v>
       </c>
       <c r="E77">
         <v>13.74</v>
       </c>
       <c r="F77">
-        <v>13.74</v>
-      </c>
-      <c r="G77">
         <v>43.4</v>
       </c>
-      <c r="H77" s="3">
+      <c r="G77" s="3">
         <f>LOOKUP(A77,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>7045.1438083273497</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
-      </c>
-      <c r="C78" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E78">
         <v>1.6</v>
       </c>
       <c r="F78">
-        <v>1.6</v>
-      </c>
-      <c r="G78">
         <v>43.4</v>
       </c>
-      <c r="H78" s="3">
+      <c r="G78" s="3">
         <f>LOOKUP(A78,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1100.3449358375769</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>74</v>
-      </c>
-      <c r="C79" t="s">
-        <v>22</v>
+        <v>68</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>5.085</v>
       </c>
       <c r="E79">
         <v>5.085</v>
       </c>
       <c r="F79">
-        <v>5.085</v>
-      </c>
-      <c r="G79">
         <v>43.4</v>
       </c>
-      <c r="H79" s="3">
+      <c r="G79" s="3">
         <f>LOOKUP(A79,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>287.74363818456021</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>74</v>
-      </c>
-      <c r="C80" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E80">
         <v>10</v>
       </c>
       <c r="F80">
-        <v>10</v>
-      </c>
-      <c r="G80">
         <v>43.4</v>
       </c>
-      <c r="H80" s="3">
+      <c r="G80" s="3">
         <f>LOOKUP(A80,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>614.5167396174337</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E81">
         <v>21</v>
       </c>
       <c r="F81">
-        <v>21</v>
-      </c>
-      <c r="G81">
         <v>43.4</v>
       </c>
-      <c r="H81" s="3">
+      <c r="G81" s="3">
         <f>LOOKUP(A81,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2993.828399940784</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>25.87</v>
       </c>
       <c r="E82">
         <v>25.87</v>
       </c>
       <c r="F82">
-        <v>25.87</v>
-      </c>
-      <c r="G82">
         <v>43.4</v>
       </c>
-      <c r="H82" s="3">
+      <c r="G82" s="3">
         <f>LOOKUP(A82,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1043.4499458197879</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>74</v>
-      </c>
-      <c r="C83" t="s">
-        <v>34</v>
+        <v>68</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>27.04</v>
       </c>
       <c r="E83">
         <v>27.04</v>
       </c>
       <c r="F83">
-        <v>27.04</v>
-      </c>
-      <c r="G83">
         <v>43.4</v>
       </c>
-      <c r="H83" s="3">
+      <c r="G83" s="3">
         <f>LOOKUP(A83,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>9739.9071363956209</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>74</v>
-      </c>
-      <c r="C84" t="s">
-        <v>22</v>
+        <v>68</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="E84">
         <v>5.54</v>
       </c>
       <c r="F84">
-        <v>5.54</v>
-      </c>
-      <c r="G84">
         <v>43.4</v>
       </c>
-      <c r="H84" s="3">
+      <c r="G84" s="3">
         <f>LOOKUP(A84,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>500.1647038676619</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
-      </c>
-      <c r="C85" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="E85">
         <v>20.7</v>
       </c>
       <c r="F85">
-        <v>20.7</v>
-      </c>
-      <c r="G85">
         <v>43.4</v>
       </c>
-      <c r="H85" s="3">
+      <c r="G85" s="3">
         <f>LOOKUP(A85,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>5830.6457879304053</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>74</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="E86">
         <v>3.5</v>
       </c>
       <c r="F86">
-        <v>3.5</v>
-      </c>
-      <c r="G86">
         <v>43.4</v>
       </c>
-      <c r="H86" s="3">
+      <c r="G86" s="3">
         <f>LOOKUP(A86,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>350.63398610770378</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>74</v>
-      </c>
-      <c r="C87" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>36.75</v>
       </c>
       <c r="E87">
         <v>36.75</v>
       </c>
       <c r="F87">
-        <v>36.75</v>
-      </c>
-      <c r="G87">
         <v>43.4</v>
       </c>
-      <c r="H87" s="3">
+      <c r="G87" s="3">
         <f>LOOKUP(A87,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>6122.4369765857291</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>19.079999999999998</v>
       </c>
       <c r="E88">
         <v>19.079999999999998</v>
       </c>
       <c r="F88">
-        <v>19.079999999999998</v>
-      </c>
-      <c r="G88">
         <v>43.4</v>
       </c>
-      <c r="H88" s="3">
+      <c r="G88" s="3">
         <f>LOOKUP(A88,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>20257.88498724798</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>74</v>
-      </c>
-      <c r="C89" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="E89">
         <v>22.9</v>
       </c>
       <c r="F89">
-        <v>22.9</v>
-      </c>
-      <c r="G89">
         <v>43.4</v>
       </c>
-      <c r="H89" s="3">
+      <c r="G89" s="3">
         <f>LOOKUP(A89,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>8347.4716027707109</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>74</v>
-      </c>
-      <c r="C90" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>26.83</v>
       </c>
       <c r="E90">
         <v>26.83</v>
       </c>
       <c r="F90">
-        <v>26.83</v>
-      </c>
-      <c r="G90">
         <v>43.4</v>
       </c>
-      <c r="H90" s="3">
+      <c r="G90" s="3">
         <f>LOOKUP(A90,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2400.4270235909471</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
-      </c>
-      <c r="C91" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="E91">
         <v>9.1</v>
       </c>
       <c r="F91">
-        <v>9.1</v>
-      </c>
-      <c r="G91">
         <v>43.4</v>
       </c>
-      <c r="H91" s="3">
+      <c r="G91" s="3">
         <f>LOOKUP(A91,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1225.552589242749</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
-      </c>
-      <c r="C92" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>15.84</v>
       </c>
       <c r="E92">
         <v>15.84</v>
       </c>
       <c r="F92">
-        <v>15.84</v>
-      </c>
-      <c r="G92">
         <v>43.4</v>
       </c>
-      <c r="H92" s="3">
+      <c r="G92" s="3">
         <f>LOOKUP(A92,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>312426.03767695627</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>74</v>
-      </c>
-      <c r="C93" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="E93">
         <v>39.299999999999997</v>
       </c>
       <c r="F93">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="G93">
         <v>43.4</v>
       </c>
-      <c r="H93" s="3">
+      <c r="G93" s="3">
         <f>LOOKUP(A93,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>9211.3752871367524</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
-      </c>
-      <c r="C94" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>3.3370000000000002</v>
       </c>
       <c r="E94">
         <v>3.3370000000000002</v>
       </c>
       <c r="F94">
-        <v>3.3370000000000002</v>
-      </c>
-      <c r="G94">
         <v>43.4</v>
       </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3">
         <f>LOOKUP(A94,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1218.450561052719</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
-      </c>
-      <c r="C95" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>22.26</v>
       </c>
       <c r="E95">
         <v>22.26</v>
       </c>
       <c r="F95">
-        <v>22.26</v>
-      </c>
-      <c r="G95">
         <v>43.4</v>
       </c>
-      <c r="H95" s="3">
+      <c r="G95" s="3">
         <f>LOOKUP(A95,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>7647.8277402915446</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>74</v>
-      </c>
-      <c r="C96" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>15.175000000000001</v>
       </c>
       <c r="E96">
         <v>15.175000000000001</v>
       </c>
       <c r="F96">
-        <v>15.175000000000001</v>
-      </c>
-      <c r="G96">
         <v>43.4</v>
       </c>
-      <c r="H96" s="3">
+      <c r="G96" s="3">
         <f>LOOKUP(A96,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1560.984478666013</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>111</v>
-      </c>
-      <c r="C97" t="s">
-        <v>22</v>
+        <v>105</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>34.273000000000003</v>
       </c>
       <c r="E97">
         <v>34.273000000000003</v>
       </c>
       <c r="F97">
-        <v>34.273000000000003</v>
-      </c>
-      <c r="G97">
         <v>31.3</v>
       </c>
-      <c r="H97" s="3">
+      <c r="G97" s="3">
         <f>LOOKUP(A97,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>255.467650523966</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
-      </c>
-      <c r="C98" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>38.198999999999998</v>
       </c>
       <c r="E98">
         <v>38.198999999999998</v>
       </c>
       <c r="F98">
-        <v>38.198999999999998</v>
-      </c>
-      <c r="G98">
         <v>31.3</v>
       </c>
-      <c r="H98" s="3">
+      <c r="G98" s="3">
         <f>LOOKUP(A98,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>350.27415493806342</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
-      </c>
-      <c r="C99" t="s">
-        <v>9</v>
+        <v>105</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>97.546999999999997</v>
       </c>
       <c r="E99">
         <v>97.546999999999997</v>
       </c>
       <c r="F99">
-        <v>97.546999999999997</v>
-      </c>
-      <c r="G99">
         <v>31.3</v>
       </c>
-      <c r="H99" s="3">
+      <c r="G99" s="3">
         <f>LOOKUP(A99,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1582.0808604981021</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
-      </c>
-      <c r="C100" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>41.19</v>
       </c>
       <c r="E100">
         <v>41.19</v>
       </c>
       <c r="F100">
-        <v>41.19</v>
-      </c>
-      <c r="G100">
         <v>31.3</v>
       </c>
-      <c r="H100" s="3">
+      <c r="G100" s="3">
         <f>LOOKUP(A100,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1582.0808604981021</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
-      </c>
-      <c r="C101" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="E101">
         <v>22.65</v>
       </c>
       <c r="F101">
-        <v>22.65</v>
-      </c>
-      <c r="G101">
         <v>31.3</v>
       </c>
-      <c r="H101" s="3">
+      <c r="G101" s="3">
         <f>LOOKUP(A101,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1303.402855759472</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
-      </c>
-      <c r="C102" t="s">
-        <v>22</v>
+        <v>105</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>8.7379999999999995</v>
       </c>
       <c r="E102">
         <v>8.7379999999999995</v>
       </c>
       <c r="F102">
-        <v>8.7379999999999995</v>
-      </c>
-      <c r="G102">
         <v>31.3</v>
       </c>
-      <c r="H102" s="3">
+      <c r="G102" s="3">
         <f>LOOKUP(A102,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2334.742487692165</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B103" t="s">
-        <v>111</v>
-      </c>
-      <c r="C103" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>14.757999999999999</v>
       </c>
       <c r="E103">
         <v>14.757999999999999</v>
       </c>
       <c r="F103">
-        <v>14.757999999999999</v>
-      </c>
-      <c r="G103">
         <v>31.3</v>
       </c>
-      <c r="H103" s="3">
+      <c r="G103" s="3">
         <f>LOOKUP(A103,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>58.698162871085799</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
-      </c>
-      <c r="C104" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>21.07</v>
       </c>
       <c r="E104">
         <v>21.07</v>
       </c>
       <c r="F104">
-        <v>21.07</v>
-      </c>
-      <c r="G104">
         <v>31.3</v>
       </c>
-      <c r="H104" s="3">
+      <c r="G104" s="3">
         <f>LOOKUP(A104,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2410.0600109964689</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
-      </c>
-      <c r="C105" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="E105">
         <v>13.5</v>
       </c>
       <c r="F105">
-        <v>13.5</v>
-      </c>
-      <c r="G105">
         <v>31.3</v>
       </c>
-      <c r="H105" s="3">
+      <c r="G105" s="3">
         <f>LOOKUP(A105,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>988.76926216579295</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B106" t="s">
-        <v>111</v>
-      </c>
-      <c r="C106" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>13.667</v>
       </c>
       <c r="E106">
         <v>13.667</v>
       </c>
       <c r="F106">
-        <v>13.667</v>
-      </c>
-      <c r="G106">
         <v>31.3</v>
       </c>
-      <c r="H106" s="3">
+      <c r="G106" s="3">
         <f>LOOKUP(A106,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>795.90900701789189</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
-      </c>
-      <c r="C107" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>15.1</v>
       </c>
       <c r="E107">
         <v>15.1</v>
       </c>
       <c r="F107">
-        <v>15.1</v>
-      </c>
-      <c r="G107">
         <v>31.3</v>
       </c>
-      <c r="H107" s="3">
+      <c r="G107" s="3">
         <f>LOOKUP(A107,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>983.96319621623854</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B108" t="s">
-        <v>111</v>
-      </c>
-      <c r="C108" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E108">
         <v>1.8</v>
       </c>
       <c r="F108">
-        <v>1.8</v>
-      </c>
-      <c r="G108">
         <v>31.3</v>
       </c>
-      <c r="H108" s="3">
+      <c r="G108" s="3">
         <f>LOOKUP(A108,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1804.664297686892</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B109" t="s">
-        <v>111</v>
-      </c>
-      <c r="C109" t="s">
-        <v>22</v>
+        <v>105</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>43.348999999999997</v>
       </c>
       <c r="E109">
         <v>43.348999999999997</v>
       </c>
       <c r="F109">
-        <v>43.348999999999997</v>
-      </c>
-      <c r="G109">
         <v>31.3</v>
       </c>
-      <c r="H109" s="3">
+      <c r="G109" s="3">
         <f>LOOKUP(A109,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>78.997025515969781</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
-      </c>
-      <c r="C110" t="s">
-        <v>9</v>
+        <v>105</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>35.898000000000003</v>
       </c>
       <c r="E110">
         <v>35.898000000000003</v>
       </c>
       <c r="F110">
-        <v>35.898000000000003</v>
-      </c>
-      <c r="G110">
         <v>31.3</v>
       </c>
-      <c r="H110" s="3">
+      <c r="G110" s="3">
         <f>LOOKUP(A110,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>15150.509101287529</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
-      </c>
-      <c r="C111" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="E111">
         <v>8.3800000000000008</v>
       </c>
       <c r="F111">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="G111">
         <v>31.3</v>
       </c>
-      <c r="H111" s="3">
+      <c r="G111" s="3">
         <f>LOOKUP(A111,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1154.3303419575391</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
-      </c>
-      <c r="C112" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>10.569000000000001</v>
       </c>
       <c r="E112">
         <v>10.569000000000001</v>
       </c>
       <c r="F112">
-        <v>10.569000000000001</v>
-      </c>
-      <c r="G112">
         <v>31.3</v>
       </c>
-      <c r="H112" s="3">
+      <c r="G112" s="3">
         <f>LOOKUP(A112,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>633.73803887257463</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
-      </c>
-      <c r="C113" t="s">
-        <v>9</v>
+        <v>105</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="E113">
         <v>13.5</v>
       </c>
       <c r="F113">
-        <v>13.5</v>
-      </c>
-      <c r="G113">
         <v>31.3</v>
       </c>
-      <c r="H113" s="3">
+      <c r="G113" s="3">
         <f>LOOKUP(A113,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1490.386832849442</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>111</v>
-      </c>
-      <c r="C114" t="s">
-        <v>22</v>
+        <v>105</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="E114">
         <v>3.5</v>
       </c>
       <c r="F114">
-        <v>3.5</v>
-      </c>
-      <c r="G114">
         <v>31.3</v>
       </c>
-      <c r="H114" s="3">
+      <c r="G114" s="3">
         <f>LOOKUP(A114,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2150.879135346036</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B115" t="s">
-        <v>44</v>
-      </c>
-      <c r="C115" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>159.477</v>
       </c>
       <c r="E115">
         <v>159.477</v>
       </c>
       <c r="F115">
-        <v>159.477</v>
-      </c>
-      <c r="G115">
         <v>43.05</v>
       </c>
-      <c r="H115" s="3">
+      <c r="G115" s="3">
         <f>LOOKUP(A115,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>2150.879135346036</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B116" t="s">
-        <v>44</v>
-      </c>
-      <c r="C116" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>5.0819999999999999</v>
       </c>
       <c r="E116">
         <v>5.0819999999999999</v>
       </c>
       <c r="F116">
-        <v>5.0819999999999999</v>
-      </c>
-      <c r="G116">
         <v>43.05</v>
       </c>
-      <c r="H116" s="3">
+      <c r="G116" s="3">
         <f>LOOKUP(A116,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>80930.84814598762</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
-      </c>
-      <c r="C117" t="s">
-        <v>9</v>
+        <v>126</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>59.9</v>
       </c>
       <c r="E117">
         <v>59.9</v>
       </c>
       <c r="F117">
-        <v>59.9</v>
-      </c>
-      <c r="G117">
         <v>43.05</v>
       </c>
-      <c r="H117" s="3">
+      <c r="G117" s="3">
         <f>LOOKUP(A117,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>457008.72116485192</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B118" t="s">
-        <v>134</v>
-      </c>
-      <c r="C118" t="s">
-        <v>9</v>
+        <v>128</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>116.286</v>
       </c>
       <c r="E118">
         <v>116.286</v>
       </c>
       <c r="F118">
-        <v>116.286</v>
-      </c>
-      <c r="G118">
         <v>31.3</v>
       </c>
-      <c r="H118" s="3">
+      <c r="G118" s="3">
         <f>LOOKUP(A118,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>4701.9144853737853</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>136</v>
-      </c>
-      <c r="C119" t="s">
-        <v>9</v>
+        <v>130</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>54.646999999999998</v>
       </c>
       <c r="E119">
         <v>54.646999999999998</v>
       </c>
       <c r="F119">
-        <v>54.646999999999998</v>
-      </c>
-      <c r="G119">
         <v>31.3</v>
       </c>
-      <c r="H119" s="3">
+      <c r="G119" s="3">
         <f>LOOKUP(A119,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>51706.683826834233</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B120" t="s">
-        <v>44</v>
-      </c>
-      <c r="C120" t="s">
-        <v>9</v>
+        <v>39</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="E120">
         <v>9.5180000000000007</v>
       </c>
       <c r="F120">
-        <v>9.5180000000000007</v>
-      </c>
-      <c r="G120">
         <v>43.05</v>
       </c>
-      <c r="H120" s="3">
+      <c r="G120" s="3">
         <f>LOOKUP(A120,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>18259.698641999999</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B121" t="s">
-        <v>74</v>
-      </c>
-      <c r="C121" t="s">
-        <v>9</v>
+        <v>68</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>6.9980000000000002</v>
       </c>
       <c r="E121">
         <v>6.9980000000000002</v>
       </c>
       <c r="F121">
-        <v>6.9980000000000002</v>
-      </c>
-      <c r="G121">
         <v>43.4</v>
       </c>
-      <c r="H121" s="3">
+      <c r="G121" s="3">
         <f>LOOKUP(A121,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>64669.007200000007</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B122" t="s">
-        <v>44</v>
-      </c>
-      <c r="C122" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>26.893000000000001</v>
       </c>
       <c r="E122">
         <v>26.893000000000001</v>
       </c>
       <c r="F122">
-        <v>26.893000000000001</v>
-      </c>
-      <c r="G122">
         <v>43.05</v>
       </c>
-      <c r="H122" s="3">
+      <c r="G122" s="3">
         <f>LOOKUP(A122,[1]Sheet1!$A$2:$A$125,[1]Sheet1!$B$2:$B$125)</f>
         <v>1082.474698389354</v>
       </c>
